--- a/data/trans_orig/IP31KM07_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM07_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>50557</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>46447</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>52765</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>94,12%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>86,47%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>98,23%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>47476</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>36740</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>51974</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>88,41%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>68,42%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>96,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>54975</t>
+          <t>42249</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50677</t>
+          <t>37647</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57265</t>
+          <t>44558</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>102451</t>
+          <t>92806</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90597</t>
+          <t>87379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107830</t>
+          <t>96130</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,5%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3158</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7268</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5,88%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>13,53%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1725</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16959</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>11,59%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>31,58%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>8258</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21446</t>
+          <t>12241</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>400733</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>380419</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>417271</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>85,92%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>81,56%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>89,46%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>566</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>386187</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>312024</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>413599</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>85,47%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>69,06%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>91,54%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>428428</t>
+          <t>383581</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>403820</t>
+          <t>370761</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>447319</t>
+          <t>393134</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>814615</t>
+          <t>784315</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>716228</t>
+          <t>760592</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>848392</t>
+          <t>804582</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>65690</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>49152</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>86004</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>14,08%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10,54%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>18,44%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>65645</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>38233</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>139808</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>30,94%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>76822</t>
+          <t>41085</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>57931</t>
+          <t>31532</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>101430</t>
+          <t>53905</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>142467</t>
+          <t>106775</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>108690</t>
+          <t>86508</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>240854</t>
+          <t>130498</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>152062</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>144424</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>157191</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>91,23%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>86,64%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>94,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>131750</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>124884</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>137363</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>85,43%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>93,96%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>164568</t>
+          <t>132617</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>156939</t>
+          <t>125578</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>170012</t>
+          <t>138319</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>296317</t>
+          <t>284678</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>286563</t>
+          <t>275327</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>304125</t>
+          <t>292442</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14624</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9495</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>22262</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>13,36%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>14436</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8823</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>21302</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>14,57%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16571</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>8821</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24200</t>
+          <t>21562</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>29147</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23199</t>
+          <t>21383</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40761</t>
+          <t>38498</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>603352</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>582763</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>619772</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>87,85%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>84,85%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>90,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>829</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>565414</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>481054</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>594348</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>86,76%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>73,81%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>91,2%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>842</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>647971</t>
+          <t>558448</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>623159</t>
+          <t>543623</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>667911</t>
+          <t>570247</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1213384</t>
+          <t>1161799</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1128604</t>
+          <t>1135000</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1246377</t>
+          <t>1183532</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>90,72%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>83472</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>67052</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>104061</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12,15%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>86303</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>57369</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>170663</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,8%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>26,19%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>96762</t>
+          <t>59263</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76822</t>
+          <t>47464</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>121574</t>
+          <t>74088</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>183066</t>
+          <t>142736</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>150073</t>
+          <t>121003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>267846</t>
+          <t>169535</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
